--- a/reports/partd_analyst_pack.xlsx
+++ b/reports/partd_analyst_pack.xlsx
@@ -485,7 +485,7 @@
     <t xml:space="preserve">Medicare negotiated prices for 2026 (first 10 drugs): exposure and early check</t>
   </si>
   <si>
-    <t xml:space="preserve">List and negotiated prices (30-day) typed in from the CMS fact sheet: https://cms.gov/files/document/fact-sheet-negotiated-prices-initial-price-applicability-year-2026.pdf</t>
+    <t xml:space="preserve">List and negotiated prices (30-day) transcribed from the CMS fact sheet: https://cms.gov/files/document/fact-sheet-negotiated-prices-initial-price-applicability-year-2026.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">List price, 30 days ($)</t>
